--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C55A9F6-6A0D-4AB7-A99A-DBD89E28E815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C63E9AE-CBB2-4F64-85F0-3875D3F4DA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 19-12-2025'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 29-01-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C63E9AE-CBB2-4F64-85F0-3875D3F4DA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE4F5A5-03D5-4D9B-8BF6-F8D254645EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 29-01-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 02-02-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE4F5A5-03D5-4D9B-8BF6-F8D254645EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E220B6-2D0A-4037-87D4-6C4F7963E712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 02-02-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 20-02-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E220B6-2D0A-4037-87D4-6C4F7963E712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F6C59C-4978-4D9D-8D4D-44F51EDF97C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 20-02-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 04-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F6C59C-4978-4D9D-8D4D-44F51EDF97C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDE3DFC-0BC8-47CD-8183-E3F65DBB5D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 04-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 06-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDE3DFC-0BC8-47CD-8183-E3F65DBB5D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A505B06-1FF2-473D-93B7-86A1B5088347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A505B06-1FF2-473D-93B7-86A1B5088347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3C1EB-09B3-4C63-9B88-703009A7202F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3C1EB-09B3-4C63-9B88-703009A7202F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA99A84-2EE4-48D1-AD38-F79DF3C29EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 06-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 09-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA99A84-2EE4-48D1-AD38-F79DF3C29EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BE999F-1C9C-4B42-824D-EDFD81900E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BE999F-1C9C-4B42-824D-EDFD81900E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BD25AB-D1BF-4AF9-88BF-CD7D96B7410D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 09-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 11-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BD25AB-D1BF-4AF9-88BF-CD7D96B7410D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F633AAB-C66F-4CBE-A9AB-6E0A4A031CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F633AAB-C66F-4CBE-A9AB-6E0A4A031CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51583BE-1F6D-4FA0-B522-77D83464BECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 11-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 20-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51583BE-1F6D-4FA0-B522-77D83464BECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36A3741-758F-44B0-AE58-F4474430F91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 20-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 25-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36A3741-758F-44B0-AE58-F4474430F91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA34BC7A-B711-4827-B737-E64C232BBB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 25-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 08-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA34BC7A-B711-4827-B737-E64C232BBB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7A026E-6DDB-41F0-B1EC-67930BE3FF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 08-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 10-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7A026E-6DDB-41F0-B1EC-67930BE3FF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7274F50D-A189-44AB-8817-45B937B4FDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7274F50D-A189-44AB-8817-45B937B4FDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2131AFA1-3FED-4CDC-BFCA-CF557B574240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 10-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 14-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2131AFA1-3FED-4CDC-BFCA-CF557B574240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC56E6C-7FE6-4FCD-AAF5-B29CF3FD16DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 14-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 24-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC56E6C-7FE6-4FCD-AAF5-B29CF3FD16DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305C1DFB-6DD9-43B5-BDAE-3D42DAA8656C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305C1DFB-6DD9-43B5-BDAE-3D42DAA8656C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963F63F3-0212-4A74-ADD3-AE31E149CB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 24-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 27-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963F63F3-0212-4A74-ADD3-AE31E149CB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81569C24-DF98-4C5F-A4E0-DB54D7E49DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 27-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 06-05-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81569C24-DF98-4C5F-A4E0-DB54D7E49DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC361315-49D8-4B4D-91E8-F0A0C8D9A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 06-05-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 01-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC361315-49D8-4B4D-91E8-F0A0C8D9A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4701034-FD25-4790-839B-39049DC6C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 01-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 02-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4701034-FD25-4790-839B-39049DC6C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1376A9BD-6C2A-4973-A786-3D3D7464D8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1376A9BD-6C2A-4973-A786-3D3D7464D8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40B2BE9-9210-4DF8-BE70-315195B7797B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 02-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 05-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C63E9AE-CBB2-4F64-85F0-3875D3F4DA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F03685-C405-4A26-93D0-156A8DF03A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6994E4D-9370-42BC-A1D0-CD44E5CFE9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D61F23-4619-4503-817C-404898B810BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D61F23-4619-4503-817C-404898B810BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B482F8D3-D81D-4870-946E-BAC92BFF8441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B482F8D3-D81D-4870-946E-BAC92BFF8441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704ED329-8798-4B6D-AE4B-CA82C2D6E0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 09-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 15-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704ED329-8798-4B6D-AE4B-CA82C2D6E0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B99AD-6E0A-4F05-87F9-E0967C606668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 15-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 22-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B99AD-6E0A-4F05-87F9-E0967C606668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02A552C-C321-4BD1-8280-DCF9C68284D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 22-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 23-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02A552C-C321-4BD1-8280-DCF9C68284D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FACBE1C-CACB-4DAF-9C21-7FBBC01DAD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B99AD-6E0A-4F05-87F9-E0967C606668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A67710-99C0-4D4E-BC95-AE63F0D78090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 22-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 23-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A67710-99C0-4D4E-BC95-AE63F0D78090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917314EF-4108-4437-96C8-6A1D0AB87A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 23-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 25-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917314EF-4108-4437-96C8-6A1D0AB87A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A04A8B-D72F-46AD-AAF1-D5442D1BD85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 25-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 30-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A04A8B-D72F-46AD-AAF1-D5442D1BD85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50C418D-6685-4276-B43C-3B3ECBCF193A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50C418D-6685-4276-B43C-3B3ECBCF193A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826EF43F-3249-4EC7-A3B7-16C69C08A740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 30-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 01-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826EF43F-3249-4EC7-A3B7-16C69C08A740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75F6277-F7CA-448A-BE91-F859FA087C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 01-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 02-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826EF43F-3249-4EC7-A3B7-16C69C08A740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B81E8E-EB42-46AD-90A4-ADB36B6CE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 01-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 03-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75F6277-F7CA-448A-BE91-F859FA087C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA1DA5B-DB54-45C3-A143-D98B85616593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 02-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 03-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA1DA5B-DB54-45C3-A143-D98B85616593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C36A043-6402-43C6-884A-1A3D73E562DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 03-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 09-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C36A043-6402-43C6-884A-1A3D73E562DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8ECC790-BF57-4051-B1BD-A3E7C65FA291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 09-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 19-08-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8ECC790-BF57-4051-B1BD-A3E7C65FA291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4F57D8-A156-41B1-9F57-20536BEE559B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 19-08-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 21-08-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4F57D8-A156-41B1-9F57-20536BEE559B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA70047-2D4F-414C-A7FE-6B3A638EA5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 21-08-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 27-08-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA70047-2D4F-414C-A7FE-6B3A638EA5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD9F2FA-DC98-4226-B54A-576DD6AFBCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 27-08-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 02-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD9F2FA-DC98-4226-B54A-576DD6AFBCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E874562-AA02-4B7C-BCDF-F63257075162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 02-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 06-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E874562-AA02-4B7C-BCDF-F63257075162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE47BD6-0C53-4707-98A0-A651099B9D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE47BD6-0C53-4707-98A0-A651099B9D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0BD14A-FB65-4B52-A568-D35517AB3F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 06-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 07-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0BD14A-FB65-4B52-A568-D35517AB3F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7454F3-64D3-492D-A4F6-F667420EE750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 07-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 09-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7454F3-64D3-492D-A4F6-F667420EE750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66612A-8732-4319-86E5-CC8E784A5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
